--- a/Додаток_2 Оцифровані дані/Processed_CairCloud_DIG/CairCloud_DIG_pan6/01_CairCloud_DIG_pan6.xlsx
+++ b/Додаток_2 Оцифровані дані/Processed_CairCloud_DIG/CairCloud_DIG_pan6/01_CairCloud_DIG_pan6.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B922B03-3498-441E-96CE-9C0BFDD5FC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="14100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
